--- a/Result/profitability/4950.xlsx
+++ b/Result/profitability/4950.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,7 +663,7 @@
         <v>-6.08</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8287500000000001</v>
+        <v>-0.7187500000000001</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
@@ -766,7 +766,7 @@
         <v>-0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8237500000000001</v>
+        <v>-0.7375000000000002</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
@@ -879,7 +879,7 @@
         <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7300000000000001</v>
+        <v>-0.6462500000000001</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -992,7 +992,7 @@
         <v>0.87</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5925000000000001</v>
+        <v>-0.5412500000000001</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1109,7 +1109,7 @@
         <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5350000000000001</v>
+        <v>-0.4887500000000001</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1230,7 +1230,7 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4825</v>
+        <v>-0.4362500000000001</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -8956,6 +8956,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4950</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>371</v>
+      </c>
+      <c r="D69" t="n">
+        <v>297</v>
+      </c>
+      <c r="E69" t="n">
+        <v>74</v>
+      </c>
+      <c r="F69" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="G69" t="n">
+        <v>43</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>11.70%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>6</v>
+      </c>
+      <c r="J69" t="n">
+        <v>49</v>
+      </c>
+      <c r="K69" t="n">
+        <v>26</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M69" t="n">
+        <v>-0.01375000000000012</v>
+      </c>
+      <c r="N69" t="n">
+        <v>15.72125</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.830000000000002</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.1009376723662438</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>13.66666666666667</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>4.020000000000001</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>0.2521957340025096</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
